--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -47,11 +47,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
+      <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="006B21A8"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD5D5"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -612,20 +612,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-49% pred | 0% hist
+50% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+          <t>Barre 57
+Reshma Sharma
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-61% pred | 0% hist
+58% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -661,7 +661,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -701,7 +701,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -709,7 +709,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -727,7 +727,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -773,7 +773,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -804,11 +804,11 @@
         <is>
           <t>Mat 57
 Anisha Shah
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -816,11 +816,11 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
-50% pred | 0% hist
+49% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -833,15 +833,22 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -859,11 +866,11 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-61% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -879,15 +886,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -897,33 +904,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -931,7 +917,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -939,23 +925,23 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
-Reshma Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -963,83 +949,83 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1047,20 +1033,41 @@
 []</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Raunak Khemuka
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -1068,67 +1075,60 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Karanvir Bhatia
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -1137,38 +1137,10 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1176,33 +1148,40 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -1211,42 +1190,35 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1254,7 +1226,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1262,8 +1234,8 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Cauveri Vikrant
@@ -1271,72 +1243,72 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1344,9 +1316,9 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1354,8 +1326,8 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -1363,16 +1335,16 @@
 []</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -1380,14 +1352,14 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1407,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1486,20 +1458,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-49% pred | 0% hist
+50% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+          <t>Barre 57
+Reshma Sharma
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -1518,16 +1490,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-61% pred | 0% hist
+58% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1535,7 +1507,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1553,7 +1525,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1575,7 +1547,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1583,7 +1555,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -1601,7 +1573,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -1610,7 +1582,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1619,19 +1591,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1647,7 +1619,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1665,7 +1637,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1678,11 +1650,11 @@
         <is>
           <t>Mat 57
 Anisha Shah
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -1690,11 +1662,11 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
-50% pred | 0% hist
+49% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1707,15 +1679,22 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -1733,11 +1712,11 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-61% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1753,15 +1732,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1771,33 +1750,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1805,7 +1763,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1813,23 +1771,23 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
-Reshma Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1837,83 +1795,83 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1921,20 +1879,41 @@
 []</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Raunak Khemuka
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -1942,67 +1921,60 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Karanvir Bhatia
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -2011,38 +1983,10 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2050,33 +1994,40 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -2085,42 +2036,35 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2128,7 +2072,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2136,8 +2080,8 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Cauveri Vikrant
@@ -2145,72 +2089,72 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2218,9 +2162,9 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2228,8 +2172,8 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2237,16 +2181,16 @@
 []</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -2254,14 +2198,14 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2281,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2360,20 +2304,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-49% pred | 0% hist
+50% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+          <t>Barre 57
+Reshma Sharma
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -2392,16 +2336,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-61% pred | 0% hist
+58% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2409,7 +2353,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2427,7 +2371,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2449,7 +2393,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2457,7 +2401,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -2475,7 +2419,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -2484,7 +2428,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2493,19 +2437,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2521,7 +2465,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2539,7 +2483,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2552,11 +2496,11 @@
         <is>
           <t>Mat 57
 Anisha Shah
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -2564,11 +2508,11 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
-50% pred | 0% hist
+49% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2581,15 +2525,22 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -2607,11 +2558,11 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-61% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2627,15 +2578,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2645,33 +2596,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2679,7 +2609,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2687,23 +2617,23 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
-Reshma Sharma
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2711,83 +2641,83 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2795,20 +2725,41 @@
 []</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Raunak Khemuka
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
       </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -2816,67 +2767,60 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Karanvir Bhatia
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -2885,38 +2829,10 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2924,33 +2840,40 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -2959,42 +2882,35 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -3002,7 +2918,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -3010,8 +2926,8 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Cauveri Vikrant
@@ -3019,72 +2935,72 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -3092,9 +3008,9 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -3102,8 +3018,8 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -3111,16 +3027,16 @@
 []</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -3128,14 +3044,14 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -47,11 +47,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="006B21A8"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
+      <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
     <font>
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD5D5"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -612,20 +612,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-50% pred | 0% hist
+48% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -661,7 +661,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -701,7 +701,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -709,7 +709,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -727,7 +727,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-69% pred | 0% hist
+67% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -773,7 +773,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -804,26 +804,19 @@
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
 33% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
@@ -833,22 +826,15 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -860,17 +846,24 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
+59% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -886,15 +879,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -911,13 +904,13 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+          <t>Barre 57
+Simran Dutt
+64% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -925,19 +918,19 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
+Reshma Sharma
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -949,7 +942,14 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -960,16 +960,9 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -991,19 +984,19 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-56% pred | 0% hist
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1011,92 +1004,106 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
+Karanvir Bhatia
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1109,107 +1116,100 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
-34% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Shruti Kulkarni
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1235,14 +1235,7 @@
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
@@ -1252,23 +1245,16 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1276,7 +1262,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1284,7 +1270,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1292,10 +1278,10 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -1308,7 +1294,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1318,7 +1304,7 @@
       </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1327,7 +1313,7 @@
         </is>
       </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -1343,7 +1329,14 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
@@ -1356,14 +1349,7 @@
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1458,20 +1444,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-50% pred | 0% hist
+48% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -1490,16 +1476,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1507,7 +1493,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1525,7 +1511,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1547,7 +1533,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1555,7 +1541,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -1573,7 +1559,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -1582,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1591,19 +1577,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-69% pred | 0% hist
+67% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1619,7 +1605,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1637,7 +1623,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1650,26 +1636,19 @@
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
 33% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
@@ -1679,22 +1658,15 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -1706,17 +1678,24 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
+59% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1732,15 +1711,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1757,13 +1736,13 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+          <t>Barre 57
+Simran Dutt
+64% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1771,19 +1750,19 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
+Reshma Sharma
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1795,7 +1774,14 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -1806,16 +1792,9 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1837,19 +1816,19 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-56% pred | 0% hist
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1857,92 +1836,106 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
+Karanvir Bhatia
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1955,107 +1948,100 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
-34% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Shruti Kulkarni
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -2064,7 +2050,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2081,14 +2067,7 @@
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
@@ -2098,23 +2077,16 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2122,7 +2094,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2130,7 +2102,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2138,10 +2110,10 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -2154,7 +2126,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2164,7 +2136,7 @@
       </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2173,7 +2145,7 @@
         </is>
       </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2189,7 +2161,14 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
@@ -2202,14 +2181,7 @@
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2304,20 +2276,20 @@
         <is>
           <t>Mat 57
 Cauveri Vikrant
-50% pred | 0% hist
+48% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -2336,16 +2308,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
+62% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2353,7 +2325,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2371,7 +2343,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2393,7 +2365,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2401,7 +2373,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -2419,7 +2391,7 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -2428,7 +2400,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2437,19 +2409,19 @@
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-69% pred | 0% hist
+67% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2465,7 +2437,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2483,7 +2455,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2496,26 +2468,19 @@
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
 33% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
@@ -2525,22 +2490,15 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
@@ -2552,17 +2510,24 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
+59% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2578,15 +2543,15 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2603,13 +2568,13 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+          <t>Barre 57
+Simran Dutt
+64% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2617,19 +2582,19 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
+Reshma Sharma
+73% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2641,7 +2606,14 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -2652,16 +2624,9 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2683,19 +2648,19 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-56% pred | 0% hist
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2703,92 +2668,106 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 0% hist
+Karanvir Bhatia
+53% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2801,107 +2780,100 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
-34% pred | 0% hist
+38% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Shruti Kulkarni
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -2910,7 +2882,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2927,14 +2899,7 @@
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
@@ -2944,23 +2909,16 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2968,7 +2926,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2976,7 +2934,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2984,10 +2942,10 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -3000,7 +2958,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -3010,7 +2968,7 @@
       </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -3019,7 +2977,7 @@
         </is>
       </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -3035,7 +2993,14 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Recovery
@@ -3048,14 +3013,7 @@
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H26" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -43,10 +43,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -58,6 +54,10 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -83,11 +83,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
@@ -104,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,18 +152,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -608,16 +608,9 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -625,7 +618,7 @@
 []</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -633,9 +626,9 @@
 []</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -643,8 +636,8 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -652,8 +645,8 @@
 []</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -661,7 +654,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -669,8 +662,8 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -678,8 +671,8 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -687,11 +680,11 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -699,9 +692,9 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -709,7 +702,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -717,17 +710,24 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -735,8 +735,8 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -744,8 +744,8 @@
 []</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -753,15 +753,15 @@
 []</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -769,11 +769,11 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -781,17 +781,17 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -799,8 +799,8 @@
 []</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -808,7 +808,7 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -816,8 +816,8 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -825,8 +825,8 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -834,11 +834,11 @@
 []</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -854,12 +854,12 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -869,25 +869,18 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -897,12 +890,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -910,7 +903,7 @@
 []</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -918,7 +911,7 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -926,7 +919,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -934,7 +927,7 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -942,7 +935,7 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -950,7 +943,7 @@
 []</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -958,11 +951,11 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -970,29 +963,29 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1004,15 +997,57 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Anmol Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -1020,15 +1055,15 @@
 []</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1036,19 +1071,19 @@
 []</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 56% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -1057,14 +1092,14 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -1072,7 +1107,7 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1080,18 +1115,18 @@
 []</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1099,7 +1134,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1107,21 +1142,21 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1129,7 +1164,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1137,15 +1172,15 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1153,15 +1188,15 @@
 []</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1169,11 +1204,11 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -1181,28 +1216,35 @@
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="8" t="inlineStr">
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1211,14 +1253,14 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1226,7 +1268,7 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1234,19 +1276,19 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1254,7 +1296,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1262,7 +1304,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1270,7 +1312,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1278,23 +1320,23 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1302,9 +1344,9 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1312,8 +1354,8 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -1321,23 +1363,23 @@
 []</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Mrigakshi Jaiswal
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -1345,11 +1387,11 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1365,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1440,16 +1482,9 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1457,7 +1492,7 @@
 []</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -1465,9 +1500,9 @@
 []</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1475,8 +1510,8 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1484,8 +1519,8 @@
 []</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1493,7 +1528,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1501,8 +1536,8 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1510,8 +1545,8 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1519,11 +1554,11 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1531,9 +1566,9 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1541,7 +1576,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -1549,17 +1584,24 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -1567,8 +1609,8 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1576,8 +1618,8 @@
 []</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -1585,15 +1627,15 @@
 []</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1601,11 +1643,11 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1613,17 +1655,17 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1631,8 +1673,8 @@
 []</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1640,7 +1682,7 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1648,8 +1690,8 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1657,8 +1699,8 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1666,11 +1708,11 @@
 []</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1678,7 +1720,7 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1686,12 +1728,12 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1701,25 +1743,18 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1729,12 +1764,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -1742,7 +1777,7 @@
 []</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1750,7 +1785,7 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -1758,7 +1793,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1766,7 +1801,7 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1774,7 +1809,7 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -1782,7 +1817,7 @@
 []</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1790,11 +1825,11 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1802,29 +1837,29 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1836,15 +1871,57 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Anmol Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -1852,15 +1929,15 @@
 []</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1868,19 +1945,19 @@
 []</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 56% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -1889,14 +1966,14 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -1904,7 +1981,7 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1912,18 +1989,18 @@
 []</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1931,7 +2008,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1939,21 +2016,21 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1961,7 +2038,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1969,15 +2046,15 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1985,15 +2062,15 @@
 []</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2001,11 +2078,11 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2013,28 +2090,35 @@
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="8" t="inlineStr">
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2043,14 +2127,14 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2058,7 +2142,7 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2066,19 +2150,19 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2086,7 +2170,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2094,7 +2178,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2102,7 +2186,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2110,23 +2194,23 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2134,9 +2218,9 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2144,8 +2228,8 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2153,23 +2237,23 @@
 []</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Mrigakshi Jaiswal
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -2177,11 +2261,11 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2197,7 +2281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2272,16 +2356,9 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2289,7 +2366,7 @@
 []</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Anisha Shah
@@ -2297,9 +2374,9 @@
 []</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2307,8 +2384,8 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2316,8 +2393,8 @@
 []</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2325,7 +2402,7 @@
 []</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2333,8 +2410,8 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2342,8 +2419,8 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2351,11 +2428,11 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2363,9 +2440,9 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2373,7 +2450,7 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -2381,17 +2458,24 @@
 []</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -2399,8 +2483,8 @@
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2408,8 +2492,8 @@
 []</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -2417,15 +2501,15 @@
 []</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2433,11 +2517,11 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2445,17 +2529,17 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2463,8 +2547,8 @@
 []</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2472,7 +2556,7 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -2480,8 +2564,8 @@
 []</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2489,8 +2573,8 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2498,11 +2582,11 @@
 []</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -2510,7 +2594,7 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2518,12 +2602,12 @@
 []</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2533,25 +2617,18 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2561,12 +2638,12 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -2574,7 +2651,7 @@
 []</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2582,7 +2659,7 @@
 []</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>FIT
 Reshma Sharma
@@ -2590,7 +2667,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -2598,7 +2675,7 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2606,7 +2683,7 @@
 []</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -2614,7 +2691,7 @@
 []</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2622,11 +2699,11 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2634,29 +2711,29 @@
 []</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2668,15 +2745,57 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Anmol Sharma
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -2684,15 +2803,15 @@
 []</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2700,19 +2819,19 @@
 []</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 56% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Reshma Sharma
@@ -2721,14 +2840,14 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -2736,7 +2855,7 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2744,18 +2863,18 @@
 []</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -2763,7 +2882,7 @@
 []</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2771,21 +2890,21 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2793,7 +2912,7 @@
 []</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2801,15 +2920,15 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2817,15 +2936,15 @@
 []</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2833,11 +2952,11 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2845,28 +2964,35 @@
 []</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="8" t="inlineStr">
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2875,14 +3001,14 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2890,7 +3016,7 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2898,19 +3024,19 @@
 []</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2918,7 +3044,7 @@
 []</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2926,7 +3052,7 @@
 []</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2934,7 +3060,7 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2942,23 +3068,23 @@
 []</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2966,9 +3092,9 @@
 []</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2976,8 +3102,8 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
@@ -2985,23 +3111,23 @@
 []</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Mrigakshi Jaiswal
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -3009,11 +3135,11 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -811,7 +811,7 @@
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
+Bret Saldanha
 33% pred | 0% hist
 []</t>
         </is>
@@ -1021,11 +1021,32 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -1391,7 +1412,14 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1685,7 +1713,7 @@
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
+Bret Saldanha
 33% pred | 0% hist
 []</t>
         </is>
@@ -1895,11 +1923,32 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -2265,7 +2314,14 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2559,7 +2615,7 @@
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
+Bret Saldanha
 33% pred | 0% hist
 []</t>
         </is>
@@ -2769,11 +2825,32 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -3139,7 +3216,14 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -848,9 +848,9 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>PowerCycle Express
 Cauveri Vikrant
-33% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1021,14 +1021,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -1204,7 +1197,7 @@
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 23% pred | 0% hist
 []</t>
         </is>
@@ -1232,7 +1225,7 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 17% pred | 0% hist
 []</t>
         </is>
@@ -1248,7 +1241,7 @@
       <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Kajol Kanchan
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1344,7 +1337,7 @@
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -1357,11 +1350,11 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-86% pred | 0% hist
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1379,7 +1372,7 @@
       <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1392,14 +1385,7 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B28" s="5" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery
@@ -1750,9 +1736,9 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>PowerCycle Express
 Cauveri Vikrant
-33% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1923,14 +1909,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -2106,7 +2085,7 @@
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 23% pred | 0% hist
 []</t>
         </is>
@@ -2134,7 +2113,7 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 17% pred | 0% hist
 []</t>
         </is>
@@ -2150,7 +2129,7 @@
       <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Kajol Kanchan
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2246,7 +2225,7 @@
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -2259,11 +2238,11 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-86% pred | 0% hist
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2281,7 +2260,7 @@
       <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2294,14 +2273,7 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B28" s="5" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery
@@ -2652,9 +2624,9 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PowerCycle
+          <t>PowerCycle Express
 Cauveri Vikrant
-33% pred | 0% hist
+28% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2825,14 +2797,7 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -3008,7 +2973,7 @@
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 23% pred | 0% hist
 []</t>
         </is>
@@ -3036,7 +3001,7 @@
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 17% pred | 0% hist
 []</t>
         </is>
@@ -3052,7 +3017,7 @@
       <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Kajol Kanchan
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -3148,7 +3113,7 @@
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
+Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -3161,11 +3126,11 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-86% pred | 0% hist
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+44% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3183,7 +3148,7 @@
       <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -3196,14 +3161,7 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B28" s="5" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Recovery

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -613,12 +613,19 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-24% pred | 0% hist
+34% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -638,7 +645,14 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -651,11 +665,18 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
+Richard D'Costa
 19% pred | 0% hist
 []</t>
         </is>
@@ -668,11 +689,11 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+29% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -706,17 +727,17 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+5% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
@@ -728,7 +749,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -738,7 +766,14 @@
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
@@ -756,24 +791,10 @@
 []</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -791,25 +812,18 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -818,7 +832,14 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="7" t="inlineStr">
@@ -832,8 +853,8 @@
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-31% pred | 0% hist
+Simonelle De Vitre
+7% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -850,15 +871,50 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -866,7 +922,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -875,26 +931,33 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Richard D'Costa
-81% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -903,57 +966,22 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Mrigakshi Jaiswal
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -962,23 +990,23 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -986,20 +1014,27 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1015,8 +1050,8 @@
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Vivaran Dhasmana
-52% pred | 0% hist
+Richard D'Costa
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1035,8 +1070,16 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Mrigakshi Jaiswal
@@ -1044,12 +1087,11 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-29% pred | 0% hist
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1065,7 +1107,7 @@
       <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
@@ -1074,50 +1116,15 @@
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Vivaran Dhasmana
@@ -1125,19 +1132,54 @@
 []</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
 20% pred | 0% hist
 []</t>
         </is>
@@ -1145,21 +1187,7 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -1167,7 +1195,7 @@
 []</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -1176,85 +1204,106 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+          <t>Cardio Barre
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Anmol Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Bret Saldanha
-26% pred | 0% hist
+17% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1263,88 +1312,95 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anmol Sharma
-33% pred | 0% hist
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-29% pred | 0% hist
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+23% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1352,126 +1408,28 @@
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-76% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Raunak Khemuka
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -1491,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1563,7 +1521,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -1571,12 +1529,19 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-24% pred | 0% hist
+34% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -1596,7 +1561,14 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -1609,11 +1581,18 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
+Richard D'Costa
 19% pred | 0% hist
 []</t>
         </is>
@@ -1626,11 +1605,11 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+29% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1664,17 +1643,17 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+5% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
@@ -1686,7 +1665,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1696,7 +1682,14 @@
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
@@ -1714,24 +1707,10 @@
 []</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1749,25 +1728,18 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -1776,7 +1748,14 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="7" t="inlineStr">
@@ -1790,8 +1769,8 @@
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-31% pred | 0% hist
+Simonelle De Vitre
+7% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1808,15 +1787,50 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -1824,7 +1838,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1833,26 +1847,33 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Richard D'Costa
-81% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1861,57 +1882,22 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Mrigakshi Jaiswal
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1920,23 +1906,23 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1944,20 +1930,27 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1973,8 +1966,8 @@
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Vivaran Dhasmana
-52% pred | 0% hist
+Richard D'Costa
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1993,8 +1986,16 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Mrigakshi Jaiswal
@@ -2002,12 +2003,11 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-29% pred | 0% hist
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2023,7 +2023,7 @@
       <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
@@ -2032,50 +2032,15 @@
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Vivaran Dhasmana
@@ -2083,19 +2048,54 @@
 []</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
 20% pred | 0% hist
 []</t>
         </is>
@@ -2103,21 +2103,7 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -2125,7 +2111,7 @@
 []</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -2134,85 +2120,106 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+          <t>Cardio Barre
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Anmol Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Bret Saldanha
-26% pred | 0% hist
+17% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2221,88 +2228,95 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anmol Sharma
-33% pred | 0% hist
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-29% pred | 0% hist
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+23% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2310,126 +2324,28 @@
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-76% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Raunak Khemuka
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
@@ -2449,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2521,7 +2437,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -2529,12 +2445,19 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-24% pred | 0% hist
+34% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -2554,7 +2477,14 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -2567,11 +2497,18 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
+Richard D'Costa
 19% pred | 0% hist
 []</t>
         </is>
@@ -2584,11 +2521,11 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+29% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2622,17 +2559,17 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+5% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
@@ -2644,7 +2581,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2654,7 +2598,14 @@
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+65% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
@@ -2672,24 +2623,10 @@
 []</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2707,25 +2644,18 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -2734,7 +2664,14 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="7" t="inlineStr">
@@ -2748,8 +2685,8 @@
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-31% pred | 0% hist
+Simonelle De Vitre
+7% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2766,15 +2703,50 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -2782,7 +2754,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2791,26 +2763,33 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Richard D'Costa
-81% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2819,57 +2798,22 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Mrigakshi Jaiswal
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2878,23 +2822,23 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2902,20 +2846,27 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+60% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2931,8 +2882,8 @@
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Vivaran Dhasmana
-52% pred | 0% hist
+Richard D'Costa
+57% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2951,8 +2902,16 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Mrigakshi Jaiswal
@@ -2960,12 +2919,11 @@
 []</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-29% pred | 0% hist
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2981,7 +2939,7 @@
       <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
+Karan Bhatia
 20% pred | 0% hist
 []</t>
         </is>
@@ -2990,50 +2948,15 @@
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Vivaran Dhasmana
@@ -3041,19 +2964,54 @@
 []</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
 20% pred | 0% hist
 []</t>
         </is>
@@ -3061,21 +3019,7 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Bret Saldanha
@@ -3083,7 +3027,7 @@
 []</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -3092,85 +3036,106 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+          <t>Cardio Barre
+Raunak Khemuka
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Anmol Sharma
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
 Bret Saldanha
-26% pred | 0% hist
+17% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3179,88 +3144,95 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karan Bhatia
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anmol Sharma
-33% pred | 0% hist
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-29% pred | 0% hist
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+23% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -3268,126 +3240,28 @@
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-76% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Raunak Khemuka
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-70% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-34% pred | 0% hist
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -645,11 +645,11 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-30% pred | 0% hist
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -673,14 +673,7 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -689,15 +682,22 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -722,68 +722,47 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Richard D'Costa
-5% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+6% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -791,58 +770,37 @@
 []</t>
         </is>
       </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -850,268 +808,268 @@
 []</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-7% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Mrigakshi Jaiswal
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Karanvir Bhatia
-60% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1123,18 +1081,25 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+Karan Bhatia
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -1147,36 +1112,78 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
           <t>FIT
-Simonelle De Vitre
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1184,18 +1191,18 @@
 []</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -1204,21 +1211,14 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -1226,106 +1226,106 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Raunak Khemuka
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Karan Bhatia
+Anmol Sharma
 34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1333,18 +1333,18 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1352,15 +1352,15 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -1368,24 +1368,31 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karan Bhatia
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1393,10 +1400,10 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -1404,36 +1411,43 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1449,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1543,7 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-34% pred | 0% hist
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1561,11 +1575,11 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-30% pred | 0% hist
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1589,14 +1603,7 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1605,15 +1612,22 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1638,68 +1652,47 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Richard D'Costa
-5% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+6% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -1707,58 +1700,37 @@
 []</t>
         </is>
       </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1766,268 +1738,268 @@
 []</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-7% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Mrigakshi Jaiswal
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Karanvir Bhatia
-60% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2039,18 +2011,25 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+Karan Bhatia
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -2063,36 +2042,78 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
           <t>FIT
-Simonelle De Vitre
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2100,18 +2121,18 @@
 []</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -2120,21 +2141,14 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -2142,106 +2156,106 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Raunak Khemuka
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Karan Bhatia
+Anmol Sharma
 34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2249,18 +2263,18 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2268,15 +2282,15 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -2284,24 +2298,31 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karan Bhatia
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -2309,10 +2330,10 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -2320,36 +2341,43 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2365,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2445,7 +2473,7 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-34% pred | 0% hist
+32% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2477,11 +2505,11 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-30% pred | 0% hist
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+26% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2505,14 +2533,7 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2521,15 +2542,22 @@
 []</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2554,68 +2582,47 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Richard D'Costa
-5% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+6% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-65% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
@@ -2623,58 +2630,37 @@
 []</t>
         </is>
       </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-67% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2682,268 +2668,268 @@
 []</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-7% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+53% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Mrigakshi Jaiswal
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+8% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-25% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Mrigakshi Jaiswal
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Karanvir Bhatia
-60% pred | 0% hist
+43% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2955,18 +2941,25 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+Karan Bhatia
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -2979,36 +2972,78 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
           <t>FIT
-Simonelle De Vitre
+Anmol Sharma
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -3016,18 +3051,18 @@
 []</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -3036,21 +3071,14 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -3058,106 +3086,106 @@
 []</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Raunak Khemuka
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Karan Bhatia
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anmol Sharma
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Karan Bhatia
+Anmol Sharma
 34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -3165,18 +3193,18 @@
 []</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -3184,15 +3212,15 @@
 []</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -3200,24 +3228,31 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karan Bhatia
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -3225,10 +3260,10 @@
 []</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -3236,36 +3271,43 @@
 []</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -612,20 +612,13 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -673,31 +666,17 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -707,16 +686,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
@@ -738,22 +717,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Richard D'Costa
-6% pred | 0% hist
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -773,34 +745,55 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-67% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -808,36 +801,15 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -857,7 +829,14 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -883,25 +862,32 @@
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+83% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -909,47 +895,40 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Mrigakshi Jaiswal
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -958,25 +937,18 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
@@ -986,12 +958,26 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Cauveri Vikrant
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1012,19 +998,12 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-43% pred | 0% hist
+          <t>FIT
+Richard D'Costa
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1035,15 +1014,22 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+91% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1079,27 +1065,27 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
 Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -1112,14 +1098,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -1128,28 +1107,14 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Anmol Sharma
+          <t>Barre 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1158,67 +1123,53 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -1226,81 +1177,109 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -1312,7 +1291,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
+Mrigakshi Jaiswal
 48% pred | 0% hist
 []</t>
         </is>
@@ -1325,14 +1304,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -1362,71 +1334,57 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>FIT
+Atulan Purohit
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
           <t>Barre 57
 Karan Bhatia
 23% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Raunak Khemuka
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1436,7 +1394,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Anmol Sharma
 20% pred | 0% hist
 []</t>
@@ -1542,20 +1500,13 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -1603,31 +1554,17 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1637,16 +1574,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
@@ -1668,22 +1605,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Richard D'Costa
-6% pred | 0% hist
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -1703,34 +1633,55 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-67% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1738,36 +1689,15 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -1787,7 +1717,14 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1813,25 +1750,32 @@
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+83% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -1839,47 +1783,40 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Mrigakshi Jaiswal
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -1888,25 +1825,18 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
@@ -1916,12 +1846,26 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Cauveri Vikrant
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1942,19 +1886,12 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-43% pred | 0% hist
+          <t>FIT
+Richard D'Costa
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1965,15 +1902,22 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+91% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2009,27 +1953,27 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
 Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -2042,14 +1986,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -2058,28 +1995,14 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Anmol Sharma
+          <t>Barre 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2088,67 +2011,53 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -2156,81 +2065,109 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -2242,7 +2179,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
+Mrigakshi Jaiswal
 48% pred | 0% hist
 []</t>
         </is>
@@ -2255,14 +2192,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -2292,71 +2222,57 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>FIT
+Atulan Purohit
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
           <t>Barre 57
 Karan Bhatia
 23% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Raunak Khemuka
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -2366,7 +2282,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Anmol Sharma
 20% pred | 0% hist
 []</t>
@@ -2472,20 +2388,13 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
+Bret Saldanha
 32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
@@ -2533,31 +2442,17 @@
 []</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2567,16 +2462,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
@@ -2598,22 +2493,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Richard D'Costa
-6% pred | 0% hist
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2633,34 +2521,55 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Atulan Purohit
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-67% pred | 0% hist
+68% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2668,36 +2577,15 @@
 []</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -2717,7 +2605,14 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2743,25 +2638,32 @@
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>FIT
+Atulan Purohit
+83% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -2769,47 +2671,40 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Bret Saldanha
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Mrigakshi Jaiswal
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -2818,25 +2713,18 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-85% pred | 0% hist
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
@@ -2846,12 +2734,26 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Cauveri Vikrant
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2872,19 +2774,12 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-43% pred | 0% hist
+          <t>FIT
+Richard D'Costa
+60% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2895,15 +2790,22 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+91% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2939,27 +2841,27 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
 Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Cauveri Vikrant
 20% pred | 0% hist
 []</t>
@@ -2972,14 +2874,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -2988,28 +2883,14 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Anmol Sharma
+          <t>Barre 57
+Reshma Sharma
 20% pred | 0% hist
 []</t>
         </is>
@@ -3018,67 +2899,53 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -3086,81 +2953,109 @@
 []</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -3172,7 +3067,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
+Mrigakshi Jaiswal
 48% pred | 0% hist
 []</t>
         </is>
@@ -3185,14 +3080,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -3222,71 +3110,57 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>FIT
+Atulan Purohit
+76% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
           <t>Barre 57
 Karan Bhatia
 23% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>PowerCycle
-Raunak Khemuka
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -3296,7 +3170,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Anmol Sharma
 20% pred | 0% hist
 []</t>
